--- a/data/datasets/features/feature_group_1.xlsx
+++ b/data/datasets/features/feature_group_1.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,85 +455,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>median_rate[t]</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>last_rate[t]</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>min_rate[t]</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>max_rate[t]</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>range_rate[t]</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>std_rate[t]</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>wavg_rate[t]</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mean_rate[t-1]</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>std_rate[t-1]</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>i_spread_30[t]</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>i_spread_31_90[t]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>i_spread_181_year[t]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>observed_inflation[t]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_close[t]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>std_close[t]</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>return_moex[t]</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>std_return_moex[t]</t>
         </is>
@@ -552,50 +522,32 @@
         <v>7.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11.59</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>0.008014374198942242</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2378.272380952381</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32.2038916755045</v>
+      </c>
       <c r="O2" t="n">
-        <v>8.460000000000001</v>
+        <v>0.01405907609363677</v>
       </c>
       <c r="P2" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.008014374198942242</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2378.272380952381</v>
-      </c>
-      <c r="T2" t="n">
-        <v>32.2038916755045</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.01405907609363677</v>
-      </c>
-      <c r="V2" t="n">
         <v>0.01004602788358254</v>
       </c>
     </row>
@@ -614,54 +566,36 @@
         <v>7.625</v>
       </c>
       <c r="F3" t="n">
-        <v>7.625</v>
+        <v>0.1282472940106444</v>
       </c>
       <c r="G3" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7.75</v>
+        <v>8.82</v>
       </c>
       <c r="J3" t="n">
-        <v>0.25</v>
+        <v>6.86</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1282472940106444</v>
+        <v>12.52</v>
       </c>
       <c r="L3" t="n">
-        <v>7.625</v>
+        <v>0.008130777007981038</v>
       </c>
       <c r="M3" t="n">
-        <v>7.5</v>
+        <v>2372.620476190476</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>43.93597096641778</v>
       </c>
       <c r="O3" t="n">
-        <v>8.82</v>
+        <v>-0.02943646336417904</v>
       </c>
       <c r="P3" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.008130777007981038</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2372.620476190476</v>
-      </c>
-      <c r="T3" t="n">
-        <v>43.93597096641778</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.02943646336417904</v>
-      </c>
-      <c r="V3" t="n">
         <v>0.00912830584663935</v>
       </c>
     </row>
@@ -682,54 +616,36 @@
         <v>7.75</v>
       </c>
       <c r="F4" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75</v>
+        <v>7.625</v>
       </c>
       <c r="H4" t="n">
-        <v>7.75</v>
+        <v>0.1282472940106444</v>
       </c>
       <c r="I4" t="n">
-        <v>7.75</v>
+        <v>7.95</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>9.92</v>
       </c>
       <c r="L4" t="n">
-        <v>7.75</v>
+        <v>0.008028646452857391</v>
       </c>
       <c r="M4" t="n">
-        <v>7.625</v>
+        <v>2455.88</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1282472940106444</v>
+        <v>40.18917594524566</v>
       </c>
       <c r="O4" t="n">
-        <v>7.95</v>
+        <v>0.0612476847954202</v>
       </c>
       <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.008028646452857391</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2455.88</v>
-      </c>
-      <c r="T4" t="n">
-        <v>40.18917594524566</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.0612476847954202</v>
-      </c>
-      <c r="V4" t="n">
         <v>0.006080206265164916</v>
       </c>
     </row>
@@ -750,54 +666,36 @@
         <v>7.75</v>
       </c>
       <c r="F5" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>7.75</v>
       </c>
       <c r="H5" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>7.75</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.91</v>
       </c>
       <c r="L5" t="n">
-        <v>7.75</v>
+        <v>0.008406167604495085</v>
       </c>
       <c r="M5" t="n">
-        <v>7.75</v>
+        <v>2498.371</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25.08011351019389</v>
       </c>
       <c r="O5" t="n">
-        <v>9.959999999999999</v>
+        <v>-0.01444660348177806</v>
       </c>
       <c r="P5" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.008406167604495085</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2498.371</v>
-      </c>
-      <c r="T5" t="n">
-        <v>25.08011351019389</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.01444660348177806</v>
-      </c>
-      <c r="V5" t="n">
         <v>0.008159771950762602</v>
       </c>
     </row>
@@ -818,54 +716,36 @@
         <v>7.75</v>
       </c>
       <c r="F6" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>7.75</v>
       </c>
       <c r="H6" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7.75</v>
+        <v>8.23</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8.07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.75</v>
+        <v>0.007983990555842979</v>
       </c>
       <c r="M6" t="n">
-        <v>7.75</v>
+        <v>2484.8475</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>15.36666106766265</v>
       </c>
       <c r="O6" t="n">
-        <v>8.23</v>
+        <v>0.00770376229313019</v>
       </c>
       <c r="P6" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.007983990555842979</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2484.8475</v>
-      </c>
-      <c r="T6" t="n">
-        <v>15.36666106766265</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.00770376229313019</v>
-      </c>
-      <c r="V6" t="n">
         <v>0.005283095376779708</v>
       </c>
     </row>
@@ -886,54 +766,36 @@
         <v>7.75</v>
       </c>
       <c r="F7" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>7.75</v>
       </c>
       <c r="H7" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.75</v>
+        <v>7.55</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>7.75</v>
+        <v>0.008391878006036579</v>
       </c>
       <c r="M7" t="n">
-        <v>7.75</v>
+        <v>2558.224090909091</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>18.08747939982141</v>
       </c>
       <c r="O7" t="n">
-        <v>7.55</v>
+        <v>0.01509965294992566</v>
       </c>
       <c r="P7" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.008391878006036579</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2558.224090909091</v>
-      </c>
-      <c r="T7" t="n">
-        <v>18.08747939982141</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.01509965294992566</v>
-      </c>
-      <c r="V7" t="n">
         <v>0.004989975440526886</v>
       </c>
     </row>
@@ -954,54 +816,36 @@
         <v>7.75</v>
       </c>
       <c r="F8" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>7.75</v>
       </c>
       <c r="H8" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.75</v>
+        <v>11.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="L8" t="n">
-        <v>7.75</v>
+        <v>0.008295288815264312</v>
       </c>
       <c r="M8" t="n">
-        <v>7.75</v>
+        <v>2591.336666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>43.58907160439783</v>
       </c>
       <c r="O8" t="n">
-        <v>11.4</v>
+        <v>0.03499118521912692</v>
       </c>
       <c r="P8" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.008295288815264312</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2591.336666666667</v>
-      </c>
-      <c r="T8" t="n">
-        <v>43.58907160439783</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.03499118521912692</v>
-      </c>
-      <c r="V8" t="n">
         <v>0.008706731602258148</v>
       </c>
     </row>
@@ -1022,54 +866,36 @@
         <v>7.625</v>
       </c>
       <c r="F9" t="n">
-        <v>7.625</v>
+        <v>0.1282472940106444</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.75</v>
+        <v>8.870000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.25</v>
+        <v>9.83</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1282472940106444</v>
+        <v>8.98</v>
       </c>
       <c r="L9" t="n">
-        <v>7.625</v>
+        <v>0.008156615765260833</v>
       </c>
       <c r="M9" t="n">
-        <v>7.75</v>
+        <v>2748.511052631579</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>22.56477931416762</v>
       </c>
       <c r="O9" t="n">
-        <v>8.870000000000001</v>
+        <v>0.01315784653818963</v>
       </c>
       <c r="P9" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.008156615765260833</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2748.511052631579</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.56477931416762</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.01315784653818963</v>
-      </c>
-      <c r="V9" t="n">
         <v>0.007745725598663074</v>
       </c>
     </row>
@@ -1090,54 +916,36 @@
         <v>7.467391304347826</v>
       </c>
       <c r="F10" t="n">
-        <v>7.5</v>
+        <v>0.08608755539377277</v>
       </c>
       <c r="G10" t="n">
-        <v>7.25</v>
+        <v>7.625</v>
       </c>
       <c r="H10" t="n">
-        <v>7.25</v>
+        <v>0.1282472940106444</v>
       </c>
       <c r="I10" t="n">
-        <v>7.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.25</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08608755539377277</v>
+        <v>9.010000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>7.467391304347826</v>
+        <v>0.007901033147613035</v>
       </c>
       <c r="M10" t="n">
-        <v>7.625</v>
+        <v>2759.329565217392</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1282472940106444</v>
+        <v>54.56095719287156</v>
       </c>
       <c r="O10" t="n">
-        <v>8.640000000000001</v>
+        <v>-0.0221205295791137</v>
       </c>
       <c r="P10" t="n">
-        <v>9.879999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>9.010000000000002</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.007901033147613035</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2759.329565217392</v>
-      </c>
-      <c r="T10" t="n">
-        <v>54.56095719287156</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.0221205295791137</v>
-      </c>
-      <c r="V10" t="n">
         <v>0.006620373888041498</v>
       </c>
     </row>
@@ -1158,54 +966,36 @@
         <v>7.25</v>
       </c>
       <c r="F11" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>7.25</v>
+        <v>7.467391304347826</v>
       </c>
       <c r="H11" t="n">
-        <v>7.25</v>
+        <v>0.08608755539377277</v>
       </c>
       <c r="I11" t="n">
-        <v>7.25</v>
+        <v>10.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>8.719999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>7.25</v>
+        <v>0.007994450384145146</v>
       </c>
       <c r="M11" t="n">
-        <v>7.467391304347826</v>
+        <v>2673.455454545454</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08608755539377277</v>
+        <v>30.14472215153229</v>
       </c>
       <c r="O11" t="n">
-        <v>10.1</v>
+        <v>0.003890936535967393</v>
       </c>
       <c r="P11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>8.719999999999999</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.007994450384145146</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2673.455454545454</v>
-      </c>
-      <c r="T11" t="n">
-        <v>30.14472215153229</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.003890936535967393</v>
-      </c>
-      <c r="V11" t="n">
         <v>0.009023169856437382</v>
       </c>
     </row>
@@ -1226,54 +1016,36 @@
         <v>7.059523809523809</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>0.1091089451179959</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.25</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.25</v>
+        <v>10.12</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1091089451179959</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>7.059523809523809</v>
+        <v>0.007872293733319324</v>
       </c>
       <c r="M12" t="n">
-        <v>7.25</v>
+        <v>2789.105238095238</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>23.29249141226573</v>
       </c>
       <c r="O12" t="n">
-        <v>9.609999999999999</v>
+        <v>-0.009314787901955057</v>
       </c>
       <c r="P12" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.007872293733319324</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2789.105238095238</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23.29249141226573</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.009314787901955057</v>
-      </c>
-      <c r="V12" t="n">
         <v>0.006837605387753504</v>
       </c>
     </row>
@@ -1294,54 +1066,36 @@
         <v>6.913043478260869</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>0.1937766939407946</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>7.059523809523809</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5</v>
+        <v>0.1091089451179959</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>11.28</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>11.25</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1937766939407946</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.913043478260869</v>
+        <v>0.007485499461442169</v>
       </c>
       <c r="M13" t="n">
-        <v>7.059523809523809</v>
+        <v>2773.500434782609</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1091089451179959</v>
+        <v>73.91438336334937</v>
       </c>
       <c r="O13" t="n">
-        <v>11.28</v>
+        <v>0.04898815802351009</v>
       </c>
       <c r="P13" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.007485499461442169</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2773.500434782609</v>
-      </c>
-      <c r="T13" t="n">
-        <v>73.91438336334937</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.04898815802351009</v>
-      </c>
-      <c r="V13" t="n">
         <v>0.007967135324941178</v>
       </c>
     </row>
@@ -1362,54 +1116,36 @@
         <v>6.5</v>
       </c>
       <c r="F14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.913043478260869</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5</v>
+        <v>0.1937766939407946</v>
       </c>
       <c r="I14" t="n">
-        <v>6.5</v>
+        <v>8.780000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>9.31</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10.09</v>
       </c>
       <c r="L14" t="n">
-        <v>6.5</v>
+        <v>0.006960347917780219</v>
       </c>
       <c r="M14" t="n">
-        <v>6.913043478260869</v>
+        <v>2945.8575</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1937766939407946</v>
+        <v>21.59687449974869</v>
       </c>
       <c r="O14" t="n">
-        <v>8.780000000000001</v>
+        <v>0.001696014196014062</v>
       </c>
       <c r="P14" t="n">
-        <v>9.31</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.006960347917780219</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2945.8575</v>
-      </c>
-      <c r="T14" t="n">
-        <v>21.59687449974869</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.001696014196014062</v>
-      </c>
-      <c r="V14" t="n">
         <v>0.006341854216422482</v>
       </c>
     </row>
@@ -1430,54 +1166,36 @@
         <v>6.363636363636363</v>
       </c>
       <c r="F15" t="n">
-        <v>6.25</v>
+        <v>0.1274117978594065</v>
       </c>
       <c r="G15" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="H15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>9.540000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25</v>
+        <v>8.41</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1274117978594065</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>6.363636363636363</v>
+        <v>0.007501542999799549</v>
       </c>
       <c r="M15" t="n">
-        <v>6.5</v>
+        <v>2982.649047619047</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>54.00208356209661</v>
       </c>
       <c r="O15" t="n">
-        <v>9.540000000000001</v>
+        <v>0.04268480545532971</v>
       </c>
       <c r="P15" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.007501542999799549</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2982.649047619047</v>
-      </c>
-      <c r="T15" t="n">
-        <v>54.00208356209661</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.04268480545532971</v>
-      </c>
-      <c r="V15" t="n">
         <v>0.005569115925732852</v>
       </c>
     </row>
@@ -1498,54 +1216,36 @@
         <v>6.25</v>
       </c>
       <c r="F16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>6.25</v>
+        <v>6.363636363636363</v>
       </c>
       <c r="H16" t="n">
-        <v>6.25</v>
+        <v>0.1274117978594065</v>
       </c>
       <c r="I16" t="n">
-        <v>6.25</v>
+        <v>8.580000000000002</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>10.23</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>10.09</v>
       </c>
       <c r="L16" t="n">
-        <v>6.25</v>
+        <v>0.006872361604873811</v>
       </c>
       <c r="M16" t="n">
-        <v>6.363636363636363</v>
+        <v>3133.9345</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1274117978594065</v>
+        <v>42.17477451036315</v>
       </c>
       <c r="O16" t="n">
-        <v>8.580000000000002</v>
+        <v>9.101636019082093e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.006872361604873811</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3133.9345</v>
-      </c>
-      <c r="T16" t="n">
-        <v>42.17477451036315</v>
-      </c>
-      <c r="U16" t="n">
-        <v>9.101636019082093e-05</v>
-      </c>
-      <c r="V16" t="n">
         <v>0.008826972650268316</v>
       </c>
     </row>
@@ -1566,54 +1266,36 @@
         <v>6.065789473684211</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>0.1131034820897157</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>6.25</v>
+        <v>12.08</v>
       </c>
       <c r="J17" t="n">
-        <v>0.25</v>
+        <v>12.16</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1131034820897157</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>6.065789473684211</v>
+        <v>0.007011987926942798</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>3063.527368421053</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>84.65857250299938</v>
       </c>
       <c r="O17" t="n">
-        <v>12.08</v>
+        <v>-0.09305597165596391</v>
       </c>
       <c r="P17" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.007011987926942798</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3063.527368421053</v>
-      </c>
-      <c r="T17" t="n">
-        <v>84.65857250299938</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.09305597165596391</v>
-      </c>
-      <c r="V17" t="n">
         <v>0.01598529435161526</v>
       </c>
     </row>
@@ -1634,54 +1316,36 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>6.065789473684211</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>0.1131034820897157</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>9.27</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9.579999999999998</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>0.006675070138181471</v>
       </c>
       <c r="M18" t="n">
-        <v>6.065789473684211</v>
+        <v>2462.514285714286</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1131034820897157</v>
+        <v>214.8514706156655</v>
       </c>
       <c r="O18" t="n">
-        <v>9.27</v>
+        <v>-0.09290721932770984</v>
       </c>
       <c r="P18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>9.579999999999998</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.006675070138181471</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2462.514285714286</v>
-      </c>
-      <c r="T18" t="n">
-        <v>214.8514706156655</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.09290721932770984</v>
-      </c>
-      <c r="V18" t="n">
         <v>0.04125177412267202</v>
       </c>
     </row>
@@ -1702,54 +1366,36 @@
         <v>5.909090909090909</v>
       </c>
       <c r="F19" t="n">
+        <v>0.1973855084879308</v>
+      </c>
+      <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="G19" t="n">
-        <v>5.5</v>
-      </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>10.48</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>11.08</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1973855084879308</v>
+        <v>9.4</v>
       </c>
       <c r="L19" t="n">
-        <v>5.909090909090909</v>
+        <v>0.006675070138181471</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>2588.827272727272</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>65.89534611660252</v>
       </c>
       <c r="O19" t="n">
-        <v>10.48</v>
+        <v>0.07153512477714741</v>
       </c>
       <c r="P19" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.006675070138181471</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2588.827272727272</v>
-      </c>
-      <c r="T19" t="n">
-        <v>65.89534611660252</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07153512477714741</v>
-      </c>
-      <c r="V19" t="n">
         <v>0.0185084518405279</v>
       </c>
     </row>
@@ -1770,54 +1416,36 @@
         <v>5.5</v>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>0.1973855084879308</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>10.01</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.79</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>9.899999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>5.5</v>
+        <v>0.006675070138181471</v>
       </c>
       <c r="M20" t="n">
-        <v>5.909090909090909</v>
+        <v>2683.665789473684</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1973855084879308</v>
+        <v>63.25260673730639</v>
       </c>
       <c r="O20" t="n">
-        <v>10.01</v>
+        <v>0.04198290051207021</v>
       </c>
       <c r="P20" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>9.899999999999999</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.006675070138181471</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2683.665789473684</v>
-      </c>
-      <c r="T20" t="n">
-        <v>63.25260673730639</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.04198290051207021</v>
-      </c>
-      <c r="V20" t="n">
         <v>0.01424545364565375</v>
       </c>
     </row>
@@ -1838,54 +1466,36 @@
         <v>5.2</v>
       </c>
       <c r="F21" t="n">
+        <v>0.4701623459816271</v>
+      </c>
+      <c r="G21" t="n">
         <v>5.5</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>9.049999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>9.92</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4701623459816271</v>
+        <v>9.83</v>
       </c>
       <c r="L21" t="n">
-        <v>5.2</v>
+        <v>0.006675070138181471</v>
       </c>
       <c r="M21" t="n">
-        <v>5.5</v>
+        <v>2766.8685</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>28.11272876624053</v>
       </c>
       <c r="O21" t="n">
-        <v>9.049999999999999</v>
+        <v>-0.002559776601314789</v>
       </c>
       <c r="P21" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.006675070138181471</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2766.8685</v>
-      </c>
-      <c r="T21" t="n">
-        <v>28.11272876624053</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.002559776601314789</v>
-      </c>
-      <c r="V21" t="n">
         <v>0.01035748406756849</v>
       </c>
     </row>
@@ -1906,54 +1516,36 @@
         <v>4.443181818181818</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>0.1072330068072219</v>
       </c>
       <c r="G22" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.25</v>
+        <v>0.4701623459816271</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>8.51</v>
       </c>
       <c r="J22" t="n">
-        <v>0.25</v>
+        <v>9.329999999999998</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1072330068072219</v>
+        <v>9.83</v>
       </c>
       <c r="L22" t="n">
-        <v>4.443181818181818</v>
+        <v>0.006675070138181471</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>2823.388181818182</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4701623459816271</v>
+        <v>52.46387615587245</v>
       </c>
       <c r="O22" t="n">
-        <v>8.51</v>
+        <v>0.04402626228579432</v>
       </c>
       <c r="P22" t="n">
-        <v>9.329999999999998</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.006675070138181471</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2823.388181818182</v>
-      </c>
-      <c r="T22" t="n">
-        <v>52.46387615587245</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.04402626228579432</v>
-      </c>
-      <c r="V22" t="n">
         <v>0.008053728349225221</v>
       </c>
     </row>
@@ -1974,54 +1566,36 @@
         <v>4.25</v>
       </c>
       <c r="F23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4.25</v>
+        <v>4.443181818181818</v>
       </c>
       <c r="H23" t="n">
-        <v>4.25</v>
+        <v>0.1072330068072219</v>
       </c>
       <c r="I23" t="n">
-        <v>4.25</v>
+        <v>9.56</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>10.04</v>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>0.007353590312176195</v>
       </c>
       <c r="M23" t="n">
-        <v>4.443181818181818</v>
+        <v>3009.748095238095</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1072330068072219</v>
+        <v>42.93564377286615</v>
       </c>
       <c r="O23" t="n">
-        <v>9.56</v>
+        <v>0.01236531432062438</v>
       </c>
       <c r="P23" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.007353590312176195</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3009.748095238095</v>
-      </c>
-      <c r="T23" t="n">
-        <v>42.93564377286615</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.01236531432062438</v>
-      </c>
-      <c r="V23" t="n">
         <v>0.009806834682388852</v>
       </c>
     </row>
@@ -2042,54 +1616,36 @@
         <v>4.25</v>
       </c>
       <c r="F24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>4.25</v>
       </c>
       <c r="H24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4.25</v>
+        <v>9.06</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>10.66</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>0.007529631614800802</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>2923.413181818182</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>33.61052405853231</v>
       </c>
       <c r="O24" t="n">
-        <v>9.06</v>
+        <v>-0.02325714285714287</v>
       </c>
       <c r="P24" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.007529631614800802</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2923.413181818182</v>
-      </c>
-      <c r="T24" t="n">
-        <v>33.61052405853231</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-0.02325714285714287</v>
-      </c>
-      <c r="V24" t="n">
         <v>0.009973711920105004</v>
       </c>
     </row>
@@ -2110,54 +1666,36 @@
         <v>4.25</v>
       </c>
       <c r="F25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>4.25</v>
       </c>
       <c r="H25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.25</v>
+        <v>9.540000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>10.16</v>
       </c>
       <c r="L25" t="n">
-        <v>4.25</v>
+        <v>0.007678909222941233</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>2810.621363636364</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>57.29735000067264</v>
       </c>
       <c r="O25" t="n">
-        <v>9.540000000000001</v>
+        <v>-0.06893556647518861</v>
       </c>
       <c r="P25" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.007678909222941233</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2810.621363636364</v>
-      </c>
-      <c r="T25" t="n">
-        <v>57.29735000067264</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.06893556647518861</v>
-      </c>
-      <c r="V25" t="n">
         <v>0.009155876774330919</v>
       </c>
     </row>
@@ -2178,54 +1716,36 @@
         <v>4.25</v>
       </c>
       <c r="F26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>4.25</v>
       </c>
       <c r="H26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.25</v>
+        <v>9.42</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>0.008533080028072959</v>
       </c>
       <c r="M26" t="n">
-        <v>4.25</v>
+        <v>3015.494</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>112.9724278145595</v>
       </c>
       <c r="O26" t="n">
-        <v>9.42</v>
+        <v>0.1351724541011272</v>
       </c>
       <c r="P26" t="n">
-        <v>8.350000000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.008533080028072959</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3015.494</v>
-      </c>
-      <c r="T26" t="n">
-        <v>112.9724278145595</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.1351724541011272</v>
-      </c>
-      <c r="V26" t="n">
         <v>0.01181724354630124</v>
       </c>
     </row>
@@ -2246,54 +1766,36 @@
         <v>4.25</v>
       </c>
       <c r="F27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>4.25</v>
       </c>
       <c r="H27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4.25</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>12.23</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>9.780000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>4.25</v>
+        <v>0.009454611167698079</v>
       </c>
       <c r="M27" t="n">
-        <v>4.25</v>
+        <v>3232.552272727272</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>42.64430380449075</v>
       </c>
       <c r="O27" t="n">
-        <v>9.550000000000001</v>
+        <v>0.04486639833025707</v>
       </c>
       <c r="P27" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9.780000000000001</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.009454611167698079</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3232.552272727272</v>
-      </c>
-      <c r="T27" t="n">
-        <v>42.64430380449075</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.04486639833025707</v>
-      </c>
-      <c r="V27" t="n">
         <v>0.009454015132036631</v>
       </c>
     </row>
@@ -2314,54 +1816,36 @@
         <v>4.25</v>
       </c>
       <c r="F28" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>4.25</v>
       </c>
       <c r="H28" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>4.25</v>
+        <v>9.67</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>12.78</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>9.940000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>4.25</v>
+        <v>0.01010361404333815</v>
       </c>
       <c r="M28" t="n">
-        <v>4.25</v>
+        <v>3412.641578947369</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>60.87358214302789</v>
       </c>
       <c r="O28" t="n">
-        <v>9.67</v>
+        <v>-0.0219160665092778</v>
       </c>
       <c r="P28" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9.940000000000001</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.01010361404333815</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3412.641578947369</v>
-      </c>
-      <c r="T28" t="n">
-        <v>60.87358214302789</v>
-      </c>
-      <c r="U28" t="n">
-        <v>-0.0219160665092778</v>
-      </c>
-      <c r="V28" t="n">
         <v>0.01122580479597159</v>
       </c>
     </row>
@@ -2382,54 +1866,36 @@
         <v>4.25</v>
       </c>
       <c r="F29" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>4.25</v>
       </c>
       <c r="H29" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4.25</v>
+        <v>9.780000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="L29" t="n">
-        <v>4.25</v>
+        <v>0.009702759251767334</v>
       </c>
       <c r="M29" t="n">
-        <v>4.25</v>
+        <v>3408.367</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>49.60067944144151</v>
       </c>
       <c r="O29" t="n">
-        <v>9.780000000000001</v>
+        <v>0.01686345764689445</v>
       </c>
       <c r="P29" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.009702759251767334</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3408.367</v>
-      </c>
-      <c r="T29" t="n">
-        <v>49.60067944144151</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.01686345764689445</v>
-      </c>
-      <c r="V29" t="n">
         <v>0.01149096205029011</v>
       </c>
     </row>
@@ -2450,54 +1916,36 @@
         <v>4.340909090909091</v>
       </c>
       <c r="F30" t="n">
+        <v>0.1230914909793327</v>
+      </c>
+      <c r="G30" t="n">
         <v>4.25</v>
       </c>
-      <c r="G30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H30" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.25</v>
+        <v>11.45</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1230914909793327</v>
+        <v>9.51</v>
       </c>
       <c r="L30" t="n">
-        <v>4.340909090909091</v>
+        <v>0.009981994816071982</v>
       </c>
       <c r="M30" t="n">
-        <v>4.25</v>
+        <v>3483.779090909091</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>56.88803137233626</v>
       </c>
       <c r="O30" t="n">
-        <v>9.800000000000001</v>
+        <v>0.04593994377111543</v>
       </c>
       <c r="P30" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.009981994816071982</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3483.779090909091</v>
-      </c>
-      <c r="T30" t="n">
-        <v>56.88803137233626</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0.04593994377111543</v>
-      </c>
-      <c r="V30" t="n">
         <v>0.01000652322859552</v>
       </c>
     </row>
@@ -2518,54 +1966,36 @@
         <v>4.613636363636363</v>
       </c>
       <c r="F31" t="n">
-        <v>4.5</v>
+        <v>0.2144660136144444</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>4.340909090909091</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>0.1230914909793327</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>12.35</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5</v>
+        <v>10.44</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2144660136144444</v>
+        <v>9.83</v>
       </c>
       <c r="L31" t="n">
-        <v>4.613636363636363</v>
+        <v>0.01138353379333767</v>
       </c>
       <c r="M31" t="n">
-        <v>4.340909090909091</v>
+        <v>3553.729545454546</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1230914909793327</v>
+        <v>37.88024557134551</v>
       </c>
       <c r="O31" t="n">
-        <v>12.35</v>
+        <v>0.004666141276923774</v>
       </c>
       <c r="P31" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.01138353379333767</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3553.729545454546</v>
-      </c>
-      <c r="T31" t="n">
-        <v>37.88024557134551</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.004666141276923774</v>
-      </c>
-      <c r="V31" t="n">
         <v>0.006994927293485055</v>
       </c>
     </row>
@@ -2586,54 +2016,36 @@
         <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>4.613636363636363</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>0.2144660136144444</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>12.39</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>12.07</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>10.13</v>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>0.01157316765141214</v>
       </c>
       <c r="M32" t="n">
-        <v>4.613636363636363</v>
+        <v>3667.3915</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2144660136144444</v>
+        <v>39.44881123884323</v>
       </c>
       <c r="O32" t="n">
-        <v>12.39</v>
+        <v>0.04037224540913176</v>
       </c>
       <c r="P32" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.01157316765141214</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3667.3915</v>
-      </c>
-      <c r="T32" t="n">
-        <v>39.44881123884323</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.04037224540913176</v>
-      </c>
-      <c r="V32" t="n">
         <v>0.007674785173122899</v>
       </c>
     </row>
@@ -2654,54 +2066,36 @@
         <v>5.272727272727272</v>
       </c>
       <c r="F33" t="n">
-        <v>5.5</v>
+        <v>0.2548235957188125</v>
       </c>
       <c r="G33" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5.5</v>
+        <v>13.04</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5</v>
+        <v>10.09</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2548235957188125</v>
+        <v>9.620000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>5.272727272727272</v>
+        <v>0.01166534419414322</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3820.791363636364</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>20.13610576041971</v>
       </c>
       <c r="O33" t="n">
-        <v>13.04</v>
+        <v>0.0205228192180289</v>
       </c>
       <c r="P33" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>9.620000000000001</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.01166534419414322</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3820.791363636364</v>
-      </c>
-      <c r="T33" t="n">
-        <v>20.13610576041971</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.0205228192180289</v>
-      </c>
-      <c r="V33" t="n">
         <v>0.006561863746099084</v>
       </c>
     </row>
@@ -2722,54 +2116,36 @@
         <v>5.727272727272728</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5</v>
+        <v>0.4289320272288887</v>
       </c>
       <c r="G34" t="n">
-        <v>6.5</v>
+        <v>5.272727272727272</v>
       </c>
       <c r="H34" t="n">
-        <v>5.5</v>
+        <v>0.2548235957188125</v>
       </c>
       <c r="I34" t="n">
-        <v>6.5</v>
+        <v>12.96</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>12.86</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4289320272288887</v>
+        <v>9.67</v>
       </c>
       <c r="L34" t="n">
-        <v>5.727272727272728</v>
+        <v>0.01282243045693265</v>
       </c>
       <c r="M34" t="n">
-        <v>5.272727272727272</v>
+        <v>3804.949090909091</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2548235957188125</v>
+        <v>65.98158407638799</v>
       </c>
       <c r="O34" t="n">
-        <v>12.96</v>
+        <v>-0.02248128719235321</v>
       </c>
       <c r="P34" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.01282243045693265</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3804.949090909091</v>
-      </c>
-      <c r="T34" t="n">
-        <v>65.98158407638799</v>
-      </c>
-      <c r="U34" t="n">
-        <v>-0.02248128719235321</v>
-      </c>
-      <c r="V34" t="n">
         <v>0.00778794830354564</v>
       </c>
     </row>
@@ -2790,54 +2166,36 @@
         <v>6.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>6.5</v>
+        <v>5.727272727272728</v>
       </c>
       <c r="H35" t="n">
-        <v>6.5</v>
+        <v>0.4289320272288887</v>
       </c>
       <c r="I35" t="n">
-        <v>6.5</v>
+        <v>10.78</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>14.14</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="L35" t="n">
-        <v>6.5</v>
+        <v>0.01280352281223962</v>
       </c>
       <c r="M35" t="n">
-        <v>5.727272727272728</v>
+        <v>3866.512727272727</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4289320272288887</v>
+        <v>44.13344107113356</v>
       </c>
       <c r="O35" t="n">
-        <v>10.78</v>
+        <v>0.03454502257068182</v>
       </c>
       <c r="P35" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.01280352281223962</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3866.512727272727</v>
-      </c>
-      <c r="T35" t="n">
-        <v>44.13344107113356</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.03454502257068182</v>
-      </c>
-      <c r="V35" t="n">
         <v>0.007682772516184841</v>
       </c>
     </row>
@@ -2858,54 +2216,36 @@
         <v>6.659090909090909</v>
       </c>
       <c r="F36" t="n">
-        <v>6.75</v>
+        <v>0.1230914909793325</v>
       </c>
       <c r="G36" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="H36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>6.75</v>
+        <v>12.73</v>
       </c>
       <c r="J36" t="n">
-        <v>0.25</v>
+        <v>8.77</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1230914909793325</v>
+        <v>9.739999999999998</v>
       </c>
       <c r="L36" t="n">
-        <v>6.659090909090909</v>
+        <v>0.0121552038504491</v>
       </c>
       <c r="M36" t="n">
-        <v>6.5</v>
+        <v>4028.552727272727</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>36.86885021284652</v>
       </c>
       <c r="O36" t="n">
-        <v>12.73</v>
+        <v>0.03336674204612433</v>
       </c>
       <c r="P36" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>9.739999999999998</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.0121552038504491</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4028.552727272727</v>
-      </c>
-      <c r="T36" t="n">
-        <v>36.86885021284652</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.03336674204612433</v>
-      </c>
-      <c r="V36" t="n">
         <v>0.007402591237495392</v>
       </c>
     </row>
@@ -2926,54 +2266,36 @@
         <v>6.928571428571429</v>
       </c>
       <c r="F37" t="n">
-        <v>6.75</v>
+        <v>0.3273268353539887</v>
       </c>
       <c r="G37" t="n">
-        <v>7.5</v>
+        <v>6.659090909090909</v>
       </c>
       <c r="H37" t="n">
-        <v>6.75</v>
+        <v>0.1230914909793325</v>
       </c>
       <c r="I37" t="n">
-        <v>7.5</v>
+        <v>13.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0.75</v>
+        <v>16.75</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3273268353539887</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>6.928571428571429</v>
+        <v>0.01263796951416052</v>
       </c>
       <c r="M37" t="n">
-        <v>6.659090909090909</v>
+        <v>4221.789047619048</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1230914909793325</v>
+        <v>53.69815768764897</v>
       </c>
       <c r="O37" t="n">
-        <v>13.9</v>
+        <v>0.01541721413558639</v>
       </c>
       <c r="P37" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.01263796951416052</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4221.789047619048</v>
-      </c>
-      <c r="T37" t="n">
-        <v>53.69815768764897</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.01541721413558639</v>
-      </c>
-      <c r="V37" t="n">
         <v>0.01000598201961041</v>
       </c>
     </row>
@@ -2994,54 +2316,36 @@
         <v>7.5</v>
       </c>
       <c r="F38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>7.5</v>
+        <v>6.928571428571429</v>
       </c>
       <c r="H38" t="n">
-        <v>7.5</v>
+        <v>0.3273268353539887</v>
       </c>
       <c r="I38" t="n">
-        <v>7.5</v>
+        <v>17.02</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>13.04</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="L38" t="n">
-        <v>7.5</v>
+        <v>0.01257850653964399</v>
       </c>
       <c r="M38" t="n">
-        <v>6.928571428571429</v>
+        <v>4071.658095238095</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3273268353539887</v>
+        <v>134.3946414712674</v>
       </c>
       <c r="O38" t="n">
-        <v>17.02</v>
+        <v>-0.07838464617942942</v>
       </c>
       <c r="P38" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.01257850653964399</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4071.658095238095</v>
-      </c>
-      <c r="T38" t="n">
-        <v>134.3946414712674</v>
-      </c>
-      <c r="U38" t="n">
-        <v>-0.07838464617942942</v>
-      </c>
-      <c r="V38" t="n">
         <v>0.01508263712784057</v>
       </c>
     </row>
@@ -3062,54 +2366,36 @@
         <v>7.909090909090909</v>
       </c>
       <c r="F39" t="n">
+        <v>0.5032362797401966</v>
+      </c>
+      <c r="G39" t="n">
         <v>7.5</v>
       </c>
-      <c r="G39" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>8.5</v>
+        <v>4.27</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>15.17</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5032362797401966</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>7.909090909090909</v>
+        <v>0.01365090615250653</v>
       </c>
       <c r="M39" t="n">
-        <v>7.5</v>
+        <v>3761.187727272727</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>97.12175789437454</v>
       </c>
       <c r="O39" t="n">
-        <v>4.27</v>
+        <v>-0.04344970941759752</v>
       </c>
       <c r="P39" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.01365090615250653</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3761.187727272727</v>
-      </c>
-      <c r="T39" t="n">
-        <v>97.12175789437454</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-0.04344970941759752</v>
-      </c>
-      <c r="V39" t="n">
         <v>0.01701681202968913</v>
       </c>
     </row>
@@ -3130,54 +2416,36 @@
         <v>8.5</v>
       </c>
       <c r="F40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
+        <v>7.909090909090909</v>
       </c>
       <c r="H40" t="n">
-        <v>8.5</v>
+        <v>0.5032362797401966</v>
       </c>
       <c r="I40" t="n">
-        <v>8.5</v>
+        <v>15.69</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>16.09</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>8.5</v>
+        <v>0.0129564836441014</v>
       </c>
       <c r="M40" t="n">
-        <v>7.909090909090909</v>
+        <v>3585.712857142857</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5032362797401966</v>
+        <v>203.2770451168273</v>
       </c>
       <c r="O40" t="n">
-        <v>15.69</v>
+        <v>-0.0836132381570408</v>
       </c>
       <c r="P40" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.0129564836441014</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3585.712857142857</v>
-      </c>
-      <c r="T40" t="n">
-        <v>203.2770451168273</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-0.0836132381570408</v>
-      </c>
-      <c r="V40" t="n">
         <v>0.0274639282932512</v>
       </c>
     </row>
@@ -3198,54 +2466,36 @@
         <v>9.574999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>9.5</v>
+        <v>2.504075625224227</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="H41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>16.06</v>
       </c>
       <c r="J41" t="n">
-        <v>11.5</v>
+        <v>10.98</v>
       </c>
       <c r="K41" t="n">
-        <v>2.504075625224227</v>
+        <v>8.73</v>
       </c>
       <c r="L41" t="n">
-        <v>9.574999999999999</v>
+        <v>0.01327368363582493</v>
       </c>
       <c r="M41" t="n">
-        <v>8.5</v>
+        <v>3343.366111111111</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>432.689869403002</v>
       </c>
       <c r="O41" t="n">
-        <v>16.06</v>
+        <v>-0.3037312191918651</v>
       </c>
       <c r="P41" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.01327368363582493</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3343.366111111111</v>
-      </c>
-      <c r="T41" t="n">
-        <v>432.689869403002</v>
-      </c>
-      <c r="U41" t="n">
-        <v>-0.3037312191918651</v>
-      </c>
-      <c r="V41" t="n">
         <v>0.09856781205616666</v>
       </c>
     </row>
@@ -3266,54 +2516,36 @@
         <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>9.574999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>2.504075625224227</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>14.56</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>7.419999999999998</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>8.350000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>20</v>
+        <v>0.01267251155110927</v>
       </c>
       <c r="M42" t="n">
-        <v>9.574999999999999</v>
+        <v>2519.728333333333</v>
       </c>
       <c r="N42" t="n">
-        <v>2.504075625224227</v>
+        <v>108.4832754698469</v>
       </c>
       <c r="O42" t="n">
-        <v>14.56</v>
+        <v>0.04847760916188038</v>
       </c>
       <c r="P42" t="n">
-        <v>7.419999999999998</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>8.350000000000001</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.01267251155110927</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2519.728333333333</v>
-      </c>
-      <c r="T42" t="n">
-        <v>108.4832754698469</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.04847760916188038</v>
-      </c>
-      <c r="V42" t="n">
         <v>0.04450020546967962</v>
       </c>
     </row>
@@ -3334,54 +2566,36 @@
         <v>17.85714285714286</v>
       </c>
       <c r="F43" t="n">
-        <v>17</v>
+        <v>1.388730149658827</v>
       </c>
       <c r="G43" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>16.09</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>5.16</v>
       </c>
       <c r="K43" t="n">
-        <v>1.388730149658827</v>
+        <v>16.18</v>
       </c>
       <c r="L43" t="n">
-        <v>17.85714285714286</v>
+        <v>0.01525601025807743</v>
       </c>
       <c r="M43" t="n">
-        <v>20</v>
+        <v>2464.659047619048</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>169.5286699618904</v>
       </c>
       <c r="O43" t="n">
-        <v>16.09</v>
+        <v>-0.1139532692670058</v>
       </c>
       <c r="P43" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.01525601025807743</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2464.659047619048</v>
-      </c>
-      <c r="T43" t="n">
-        <v>169.5286699618904</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-0.1139532692670058</v>
-      </c>
-      <c r="V43" t="n">
         <v>0.02732218260522392</v>
       </c>
     </row>
@@ -3402,54 +2616,36 @@
         <v>13.5</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>1.150447483271056</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>1.388730149658827</v>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>18.23</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>18.16</v>
       </c>
       <c r="K44" t="n">
-        <v>1.150447483271056</v>
+        <v>18.74</v>
       </c>
       <c r="L44" t="n">
-        <v>13.5</v>
+        <v>0.01883213580030252</v>
       </c>
       <c r="M44" t="n">
-        <v>17.85714285714286</v>
+        <v>2373.321666666667</v>
       </c>
       <c r="N44" t="n">
-        <v>1.388730149658827</v>
+        <v>48.37493508127584</v>
       </c>
       <c r="O44" t="n">
-        <v>18.23</v>
+        <v>-0.007336209947917505</v>
       </c>
       <c r="P44" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.01883213580030252</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2373.321666666667</v>
-      </c>
-      <c r="T44" t="n">
-        <v>48.37493508127584</v>
-      </c>
-      <c r="U44" t="n">
-        <v>-0.007336209947917505</v>
-      </c>
-      <c r="V44" t="n">
         <v>0.02043265301419003</v>
       </c>
     </row>
@@ -3470,54 +2666,36 @@
         <v>10.07142857142857</v>
       </c>
       <c r="F45" t="n">
-        <v>9.5</v>
+        <v>0.746420027292179</v>
       </c>
       <c r="G45" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="H45" t="n">
-        <v>9.5</v>
+        <v>1.150447483271056</v>
       </c>
       <c r="I45" t="n">
-        <v>11</v>
+        <v>26.49</v>
       </c>
       <c r="J45" t="n">
-        <v>1.5</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>0.746420027292179</v>
+        <v>13.53</v>
       </c>
       <c r="L45" t="n">
-        <v>10.07142857142857</v>
+        <v>0.01788860903783429</v>
       </c>
       <c r="M45" t="n">
-        <v>13.5</v>
+        <v>2341.398571428571</v>
       </c>
       <c r="N45" t="n">
-        <v>1.150447483271056</v>
+        <v>54.91117056535166</v>
       </c>
       <c r="O45" t="n">
-        <v>26.49</v>
+        <v>-0.07148572391139563</v>
       </c>
       <c r="P45" t="n">
-        <v>7.199999999999999</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.01788860903783429</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2341.398571428571</v>
-      </c>
-      <c r="T45" t="n">
-        <v>54.91117056535166</v>
-      </c>
-      <c r="U45" t="n">
-        <v>-0.07148572391139563</v>
-      </c>
-      <c r="V45" t="n">
         <v>0.02007041179296356</v>
       </c>
     </row>
@@ -3538,54 +2716,36 @@
         <v>9.142857142857142</v>
       </c>
       <c r="F46" t="n">
-        <v>9.5</v>
+        <v>0.6546536707079774</v>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>10.07142857142857</v>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>0.746420027292179</v>
       </c>
       <c r="I46" t="n">
-        <v>9.5</v>
+        <v>10.33</v>
       </c>
       <c r="J46" t="n">
-        <v>1.5</v>
+        <v>14.65</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6546536707079774</v>
+        <v>11.25</v>
       </c>
       <c r="L46" t="n">
-        <v>9.142857142857142</v>
+        <v>0.01683222012101293</v>
       </c>
       <c r="M46" t="n">
-        <v>10.07142857142857</v>
+        <v>2150.736190476191</v>
       </c>
       <c r="N46" t="n">
-        <v>0.746420027292179</v>
+        <v>63.44741787308514</v>
       </c>
       <c r="O46" t="n">
-        <v>10.33</v>
+        <v>0.003262923670245277</v>
       </c>
       <c r="P46" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.01683222012101293</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2150.736190476191</v>
-      </c>
-      <c r="T46" t="n">
-        <v>63.44741787308514</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.003262923670245277</v>
-      </c>
-      <c r="V46" t="n">
         <v>0.01472871772618316</v>
       </c>
     </row>
@@ -3606,54 +2766,36 @@
         <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>8</v>
+        <v>9.142857142857142</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>0.6546536707079774</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>20.03</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>22.88</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>11.19</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>0.01568198511428576</v>
       </c>
       <c r="M47" t="n">
-        <v>9.142857142857142</v>
+        <v>2194.585652173913</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6546536707079774</v>
+        <v>79.61598747773803</v>
       </c>
       <c r="O47" t="n">
-        <v>20.03</v>
+        <v>0.1009086780820974</v>
       </c>
       <c r="P47" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.01568198511428576</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2194.585652173913</v>
-      </c>
-      <c r="T47" t="n">
-        <v>79.61598747773803</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.1009086780820974</v>
-      </c>
-      <c r="V47" t="n">
         <v>0.01527250356872139</v>
       </c>
     </row>
@@ -3674,54 +2816,36 @@
         <v>7.772727272727272</v>
       </c>
       <c r="F48" t="n">
+        <v>0.2548235957188127</v>
+      </c>
+      <c r="G48" t="n">
         <v>8</v>
       </c>
-      <c r="G48" t="n">
-        <v>7.5</v>
-      </c>
       <c r="H48" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>27.22</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2548235957188127</v>
+        <v>10.35</v>
       </c>
       <c r="L48" t="n">
-        <v>7.772727272727272</v>
+        <v>0.01637208664483558</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>2276.477272727273</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>211.5637803455793</v>
       </c>
       <c r="O48" t="n">
-        <v>27.22</v>
+        <v>-0.1997162447818069</v>
       </c>
       <c r="P48" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.01637208664483558</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2276.477272727273</v>
-      </c>
-      <c r="T48" t="n">
-        <v>211.5637803455793</v>
-      </c>
-      <c r="U48" t="n">
-        <v>-0.1997162447818069</v>
-      </c>
-      <c r="V48" t="n">
         <v>0.02923209834093561</v>
       </c>
     </row>
@@ -3742,54 +2866,36 @@
         <v>7.5</v>
       </c>
       <c r="F49" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>7.5</v>
+        <v>7.772727272727272</v>
       </c>
       <c r="H49" t="n">
-        <v>7.5</v>
+        <v>0.2548235957188127</v>
       </c>
       <c r="I49" t="n">
-        <v>7.5</v>
+        <v>24.56</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>24.06</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7.5</v>
+        <v>0.01406326044273043</v>
       </c>
       <c r="M49" t="n">
-        <v>7.772727272727272</v>
+        <v>2034.042857142857</v>
       </c>
       <c r="N49" t="n">
-        <v>0.2548235957188127</v>
+        <v>78.44585024989263</v>
       </c>
       <c r="O49" t="n">
-        <v>24.56</v>
+        <v>0.06104429077944729</v>
       </c>
       <c r="P49" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.01406326044273043</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2034.042857142857</v>
-      </c>
-      <c r="T49" t="n">
-        <v>78.44585024989263</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.06104429077944729</v>
-      </c>
-      <c r="V49" t="n">
         <v>0.01922782870904712</v>
       </c>
     </row>
@@ -3810,54 +2916,36 @@
         <v>7.5</v>
       </c>
       <c r="F50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>7.5</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>27.27</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="L50" t="n">
-        <v>7.5</v>
+        <v>0.01362340760317871</v>
       </c>
       <c r="M50" t="n">
-        <v>7.5</v>
+        <v>2197.44</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>23.5576270027352</v>
       </c>
       <c r="O50" t="n">
-        <v>27.27</v>
+        <v>8.278336054456936e-05</v>
       </c>
       <c r="P50" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.01362340760317871</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2197.44</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.5576270027352</v>
-      </c>
-      <c r="U50" t="n">
-        <v>8.278336054456936e-05</v>
-      </c>
-      <c r="V50" t="n">
         <v>0.01107646859560671</v>
       </c>
     </row>
@@ -3878,54 +2966,36 @@
         <v>7.5</v>
       </c>
       <c r="F51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>7.5</v>
       </c>
       <c r="H51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>7.5</v>
+        <v>10.78</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>13.62</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="L51" t="n">
-        <v>7.5</v>
+        <v>0.0126583624938903</v>
       </c>
       <c r="M51" t="n">
-        <v>7.5</v>
+        <v>2156.263636363637</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>28.4469423489471</v>
       </c>
       <c r="O51" t="n">
-        <v>10.78</v>
+        <v>-0.01516488440033104</v>
       </c>
       <c r="P51" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.0126583624938903</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2156.263636363637</v>
-      </c>
-      <c r="T51" t="n">
-        <v>28.4469423489471</v>
-      </c>
-      <c r="U51" t="n">
-        <v>-0.01516488440033104</v>
-      </c>
-      <c r="V51" t="n">
         <v>0.005857695718131788</v>
       </c>
     </row>
@@ -3946,54 +3016,36 @@
         <v>7.5</v>
       </c>
       <c r="F52" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>7.5</v>
       </c>
       <c r="H52" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7.5</v>
+        <v>27.33</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>25.78</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>10.73</v>
       </c>
       <c r="L52" t="n">
-        <v>7.5</v>
+        <v>0.01160510231102285</v>
       </c>
       <c r="M52" t="n">
-        <v>7.5</v>
+        <v>2181.810952380952</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>20.45912336948042</v>
       </c>
       <c r="O52" t="n">
-        <v>27.33</v>
+        <v>0.02435701529907774</v>
       </c>
       <c r="P52" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.01160510231102285</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2181.810952380952</v>
-      </c>
-      <c r="T52" t="n">
-        <v>20.45912336948042</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0.02435701529907774</v>
-      </c>
-      <c r="V52" t="n">
         <v>0.007329908801977214</v>
       </c>
     </row>
@@ -4014,54 +3066,36 @@
         <v>7.5</v>
       </c>
       <c r="F53" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>7.5</v>
       </c>
       <c r="H53" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7.5</v>
+        <v>27.18</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="L53" t="n">
-        <v>7.5</v>
+        <v>0.01172474029370796</v>
       </c>
       <c r="M53" t="n">
-        <v>7.5</v>
+        <v>2228.133157894737</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>37.15737642524034</v>
       </c>
       <c r="O53" t="n">
-        <v>27.18</v>
+        <v>0.01031769163509177</v>
       </c>
       <c r="P53" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0.01172474029370796</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2228.133157894737</v>
-      </c>
-      <c r="T53" t="n">
-        <v>37.15737642524034</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.01031769163509177</v>
-      </c>
-      <c r="V53" t="n">
         <v>0.01014576812291071</v>
       </c>
     </row>
@@ -4082,54 +3116,36 @@
         <v>7.5</v>
       </c>
       <c r="F54" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>7.5</v>
       </c>
       <c r="H54" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.5</v>
+        <v>25.58</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>25.52</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>7.5</v>
+        <v>0.01118348023838589</v>
       </c>
       <c r="M54" t="n">
-        <v>7.5</v>
+        <v>2345.205909090909</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>76.82808152647661</v>
       </c>
       <c r="O54" t="n">
-        <v>25.58</v>
+        <v>0.07502028820213624</v>
       </c>
       <c r="P54" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.01118348023838589</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2345.205909090909</v>
-      </c>
-      <c r="T54" t="n">
-        <v>76.82808152647661</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0.07502028820213624</v>
-      </c>
-      <c r="V54" t="n">
         <v>0.01145064578895998</v>
       </c>
     </row>
@@ -4150,54 +3166,36 @@
         <v>7.5</v>
       </c>
       <c r="F55" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>7.5</v>
       </c>
       <c r="H55" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>7.5</v>
+        <v>26.9</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>10.11</v>
       </c>
       <c r="L55" t="n">
-        <v>7.5</v>
+        <v>0.01163548500161182</v>
       </c>
       <c r="M55" t="n">
-        <v>7.5</v>
+        <v>2571.986</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>59.99674415727684</v>
       </c>
       <c r="O55" t="n">
-        <v>26.9</v>
+        <v>0.06534536574321148</v>
       </c>
       <c r="P55" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.01163548500161182</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2571.986</v>
-      </c>
-      <c r="T55" t="n">
-        <v>59.99674415727684</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0.06534536574321148</v>
-      </c>
-      <c r="V55" t="n">
         <v>0.006556948109287463</v>
       </c>
     </row>
@@ -4218,54 +3216,36 @@
         <v>7.5</v>
       </c>
       <c r="F56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>7.5</v>
       </c>
       <c r="H56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>7.5</v>
+        <v>25.94</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>26.03</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>10.57</v>
       </c>
       <c r="L56" t="n">
-        <v>7.5</v>
+        <v>0.01106269242654978</v>
       </c>
       <c r="M56" t="n">
-        <v>7.5</v>
+        <v>2617.182380952381</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>62.33040741923354</v>
       </c>
       <c r="O56" t="n">
-        <v>25.94</v>
+        <v>0.05314065824197534</v>
       </c>
       <c r="P56" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.01106269242654978</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2617.182380952381</v>
-      </c>
-      <c r="T56" t="n">
-        <v>62.33040741923354</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.05314065824197534</v>
-      </c>
-      <c r="V56" t="n">
         <v>0.01108228186258304</v>
       </c>
     </row>
@@ -4286,54 +3266,36 @@
         <v>7.5</v>
       </c>
       <c r="F57" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>7.5</v>
       </c>
       <c r="H57" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>7.5</v>
+        <v>27.33</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>10.55</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>10.42</v>
       </c>
       <c r="L57" t="n">
-        <v>7.5</v>
+        <v>0.01088235925124281</v>
       </c>
       <c r="M57" t="n">
-        <v>7.5</v>
+        <v>2762.37380952381</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>46.1433079087522</v>
       </c>
       <c r="O57" t="n">
-        <v>27.33</v>
+        <v>0.02779114754218814</v>
       </c>
       <c r="P57" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.01088235925124281</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2762.37380952381</v>
-      </c>
-      <c r="T57" t="n">
-        <v>46.1433079087522</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.02779114754218814</v>
-      </c>
-      <c r="V57" t="n">
         <v>0.007154773771056045</v>
       </c>
     </row>
@@ -4354,54 +3316,36 @@
         <v>7.785714285714286</v>
       </c>
       <c r="F58" t="n">
+        <v>0.4629100498862758</v>
+      </c>
+      <c r="G58" t="n">
         <v>7.5</v>
       </c>
-      <c r="G58" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H58" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>8.5</v>
+        <v>15.22</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>25.79</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4629100498862758</v>
+        <v>10.03</v>
       </c>
       <c r="L58" t="n">
-        <v>7.785714285714286</v>
+        <v>0.0108375906924234</v>
       </c>
       <c r="M58" t="n">
-        <v>7.5</v>
+        <v>2908.158095238095</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>74.05223836043339</v>
       </c>
       <c r="O58" t="n">
-        <v>15.22</v>
+        <v>0.1000633516229827</v>
       </c>
       <c r="P58" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.0108375906924234</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2908.158095238095</v>
-      </c>
-      <c r="T58" t="n">
-        <v>74.05223836043339</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1000633516229827</v>
-      </c>
-      <c r="V58" t="n">
         <v>0.006923863932131116</v>
       </c>
     </row>
@@ -4422,54 +3366,36 @@
         <v>10.47826086956522</v>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>1.774044306543957</v>
       </c>
       <c r="G59" t="n">
-        <v>12</v>
+        <v>7.785714285714286</v>
       </c>
       <c r="H59" t="n">
-        <v>8.5</v>
+        <v>0.4629100498862758</v>
       </c>
       <c r="I59" t="n">
-        <v>12</v>
+        <v>24.4</v>
       </c>
       <c r="J59" t="n">
-        <v>3.5</v>
+        <v>23.35</v>
       </c>
       <c r="K59" t="n">
-        <v>1.774044306543957</v>
+        <v>9.209999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>10.47826086956522</v>
+        <v>0.01057987722739018</v>
       </c>
       <c r="M59" t="n">
-        <v>7.785714285714286</v>
+        <v>3133.713043478261</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4629100498862758</v>
+        <v>48.40143690905931</v>
       </c>
       <c r="O59" t="n">
-        <v>24.4</v>
+        <v>0.04342780672605739</v>
       </c>
       <c r="P59" t="n">
-        <v>23.35</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>9.209999999999999</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.01057987722739018</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3133.713043478261</v>
-      </c>
-      <c r="T59" t="n">
-        <v>48.40143690905931</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.04342780672605739</v>
-      </c>
-      <c r="V59" t="n">
         <v>0.00951787448053463</v>
       </c>
     </row>
@@ -4490,54 +3416,36 @@
         <v>12.47619047619048</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>0.5117663157191586</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>10.47826086956522</v>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>1.774044306543957</v>
       </c>
       <c r="I60" t="n">
-        <v>13</v>
+        <v>29.17</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>7.299999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5117663157191586</v>
+        <v>8.459999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>12.47619047619048</v>
+        <v>0.01079650282484135</v>
       </c>
       <c r="M60" t="n">
-        <v>10.47826086956522</v>
+        <v>3133.929047619047</v>
       </c>
       <c r="N60" t="n">
-        <v>1.774044306543957</v>
+        <v>73.1724213693083</v>
       </c>
       <c r="O60" t="n">
-        <v>29.17</v>
+        <v>-0.03035573367168509</v>
       </c>
       <c r="P60" t="n">
-        <v>7.299999999999999</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>8.459999999999999</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.01079650282484135</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3133.929047619047</v>
-      </c>
-      <c r="T60" t="n">
-        <v>73.1724213693083</v>
-      </c>
-      <c r="U60" t="n">
-        <v>-0.03035573367168509</v>
-      </c>
-      <c r="V60" t="n">
         <v>0.009992448196891199</v>
       </c>
     </row>
@@ -4558,54 +3466,36 @@
         <v>13.18181818181818</v>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>0.5884898863364998</v>
       </c>
       <c r="G61" t="n">
-        <v>15</v>
+        <v>12.47619047619048</v>
       </c>
       <c r="H61" t="n">
-        <v>13</v>
+        <v>0.5117663157191586</v>
       </c>
       <c r="I61" t="n">
-        <v>15</v>
+        <v>25.24</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>21.77</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5884898863364998</v>
+        <v>7.500000000000002</v>
       </c>
       <c r="L61" t="n">
-        <v>13.18181818181818</v>
+        <v>0.01087562686136523</v>
       </c>
       <c r="M61" t="n">
-        <v>12.47619047619048</v>
+        <v>3205.678181818182</v>
       </c>
       <c r="N61" t="n">
-        <v>0.5117663157191586</v>
+        <v>48.35471214900374</v>
       </c>
       <c r="O61" t="n">
-        <v>25.24</v>
+        <v>0.02191339992912611</v>
       </c>
       <c r="P61" t="n">
-        <v>21.77</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>7.500000000000002</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.01087562686136523</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3205.678181818182</v>
-      </c>
-      <c r="T61" t="n">
-        <v>48.35471214900374</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.02191339992912611</v>
-      </c>
-      <c r="V61" t="n">
         <v>0.005553043853541538</v>
       </c>
     </row>
@@ -4626,54 +3516,36 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>15</v>
+        <v>13.18181818181818</v>
       </c>
       <c r="H62" t="n">
-        <v>15</v>
+        <v>0.5884898863364998</v>
       </c>
       <c r="I62" t="n">
-        <v>15</v>
+        <v>29.89</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>8.84</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>6.079999999999998</v>
       </c>
       <c r="L62" t="n">
-        <v>15</v>
+        <v>0.0118021176538321</v>
       </c>
       <c r="M62" t="n">
-        <v>13.18181818181818</v>
+        <v>3214.292727272727</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5884898863364998</v>
+        <v>23.26544692842219</v>
       </c>
       <c r="O62" t="n">
-        <v>29.89</v>
+        <v>-0.01270224417748833</v>
       </c>
       <c r="P62" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>6.079999999999998</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.0118021176538321</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3214.292727272727</v>
-      </c>
-      <c r="T62" t="n">
-        <v>23.26544692842219</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-0.01270224417748833</v>
-      </c>
-      <c r="V62" t="n">
         <v>0.004823547712956068</v>
       </c>
     </row>
@@ -4694,54 +3566,36 @@
         <v>15.47619047619048</v>
       </c>
       <c r="F63" t="n">
+        <v>0.5117663157191586</v>
+      </c>
+      <c r="G63" t="n">
         <v>15</v>
       </c>
-      <c r="G63" t="n">
-        <v>16</v>
-      </c>
       <c r="H63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>23.95</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5117663157191586</v>
+        <v>5.579999999999998</v>
       </c>
       <c r="L63" t="n">
-        <v>15.47619047619048</v>
+        <v>0.01319854398093612</v>
       </c>
       <c r="M63" t="n">
-        <v>15</v>
+        <v>3079.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>36.1086280548016</v>
       </c>
       <c r="O63" t="n">
-        <v>9.949999999999999</v>
+        <v>-0.01374157063797421</v>
       </c>
       <c r="P63" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>5.579999999999998</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.01319854398093612</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3079.2</v>
-      </c>
-      <c r="T63" t="n">
-        <v>36.1086280548016</v>
-      </c>
-      <c r="U63" t="n">
-        <v>-0.01374157063797421</v>
-      </c>
-      <c r="V63" t="n">
         <v>0.007902074550866342</v>
       </c>
     </row>
@@ -4762,54 +3616,36 @@
         <v>16</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>16</v>
+        <v>15.47619047619048</v>
       </c>
       <c r="H64" t="n">
-        <v>16</v>
+        <v>0.5117663157191586</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>25.34</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="L64" t="n">
-        <v>16</v>
+        <v>0.01268992279066627</v>
       </c>
       <c r="M64" t="n">
-        <v>15.47619047619048</v>
+        <v>3169.565714285714</v>
       </c>
       <c r="N64" t="n">
-        <v>0.5117663157191586</v>
+        <v>20.23339753265078</v>
       </c>
       <c r="O64" t="n">
-        <v>25.34</v>
+        <v>0.02682231018168002</v>
       </c>
       <c r="P64" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.01268992279066627</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3169.565714285714</v>
-      </c>
-      <c r="T64" t="n">
-        <v>20.23339753265078</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0.02682231018168002</v>
-      </c>
-      <c r="V64" t="n">
         <v>0.00367085582850395</v>
       </c>
     </row>
@@ -4830,54 +3666,36 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>16</v>
       </c>
       <c r="H65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>27.82</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>10.81</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>6.079999999999998</v>
       </c>
       <c r="L65" t="n">
-        <v>16</v>
+        <v>0.01185439844069469</v>
       </c>
       <c r="M65" t="n">
-        <v>16</v>
+        <v>3228.5705</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>34.23519910313906</v>
       </c>
       <c r="O65" t="n">
-        <v>27.82</v>
+        <v>0.008331553086947219</v>
       </c>
       <c r="P65" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>6.079999999999998</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0.01185439844069469</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3228.5705</v>
-      </c>
-      <c r="T65" t="n">
-        <v>34.23519910313906</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0.008331553086947219</v>
-      </c>
-      <c r="V65" t="n">
         <v>0.008436902185629019</v>
       </c>
     </row>
@@ -4898,54 +3716,36 @@
         <v>16</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>16</v>
       </c>
       <c r="H66" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25.84</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>23.64</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>6.130000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>16</v>
+        <v>0.01160480870949199</v>
       </c>
       <c r="M66" t="n">
-        <v>16</v>
+        <v>3298.3165</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>20.93050714174242</v>
       </c>
       <c r="O66" t="n">
-        <v>25.84</v>
+        <v>0.02016432686597325</v>
       </c>
       <c r="P66" t="n">
-        <v>23.64</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>6.130000000000001</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.01160480870949199</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3298.3165</v>
-      </c>
-      <c r="T66" t="n">
-        <v>20.93050714174242</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0.02016432686597325</v>
-      </c>
-      <c r="V66" t="n">
         <v>0.004507068641549324</v>
       </c>
     </row>
@@ -4966,54 +3766,36 @@
         <v>16</v>
       </c>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>16</v>
       </c>
       <c r="H67" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>29.73</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>6.020000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>16</v>
+        <v>0.01127597440704098</v>
       </c>
       <c r="M67" t="n">
-        <v>16</v>
+        <v>3437.666956521739</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>33.48006156109032</v>
       </c>
       <c r="O67" t="n">
-        <v>29.73</v>
+        <v>0.03167731596145429</v>
       </c>
       <c r="P67" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>6.020000000000001</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.01127597440704098</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3437.666956521739</v>
-      </c>
-      <c r="T67" t="n">
-        <v>33.48006156109032</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0.03167731596145429</v>
-      </c>
-      <c r="V67" t="n">
         <v>0.004640143868948452</v>
       </c>
     </row>
@@ -5034,54 +3816,36 @@
         <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>16</v>
       </c>
       <c r="H68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>24.39</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>24.31</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>16</v>
+        <v>0.01100183258734555</v>
       </c>
       <c r="M68" t="n">
-        <v>16</v>
+        <v>3410.02</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>77.49924683505</v>
       </c>
       <c r="O68" t="n">
-        <v>24.39</v>
+        <v>-0.06553910590996359</v>
       </c>
       <c r="P68" t="n">
-        <v>24.31</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>7.140000000000001</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.01100183258734555</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3410.02</v>
-      </c>
-      <c r="T68" t="n">
-        <v>77.49924683505</v>
-      </c>
-      <c r="U68" t="n">
-        <v>-0.06553910590996359</v>
-      </c>
-      <c r="V68" t="n">
         <v>0.00911906705470609</v>
       </c>
     </row>
@@ -5102,54 +3866,36 @@
         <v>16</v>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>16</v>
       </c>
       <c r="H69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>29.77</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>11.03</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>16</v>
+        <v>0.01128989574866712</v>
       </c>
       <c r="M69" t="n">
-        <v>16</v>
+        <v>3154.45947368421</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>49.15604862450037</v>
       </c>
       <c r="O69" t="n">
-        <v>29.77</v>
+        <v>0.004119156305110394</v>
       </c>
       <c r="P69" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>5.600000000000001</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.01128989574866712</v>
-      </c>
-      <c r="S69" t="n">
-        <v>3154.45947368421</v>
-      </c>
-      <c r="T69" t="n">
-        <v>49.15604862450037</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0.004119156305110394</v>
-      </c>
-      <c r="V69" t="n">
         <v>0.01501736629962732</v>
       </c>
     </row>
@@ -5170,54 +3916,36 @@
         <v>16.26086956521739</v>
       </c>
       <c r="F70" t="n">
+        <v>0.6887004431501822</v>
+      </c>
+      <c r="G70" t="n">
         <v>16</v>
       </c>
-      <c r="G70" t="n">
-        <v>18</v>
-      </c>
       <c r="H70" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>12.66</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>26.41</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6887004431501822</v>
+        <v>5.489999999999998</v>
       </c>
       <c r="L70" t="n">
-        <v>16.26086956521739</v>
+        <v>0.01115788972180143</v>
       </c>
       <c r="M70" t="n">
-        <v>16</v>
+        <v>3032.401304347826</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>94.29217051775099</v>
       </c>
       <c r="O70" t="n">
-        <v>12.66</v>
+        <v>-0.07642670399442597</v>
       </c>
       <c r="P70" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>5.489999999999998</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.01115788972180143</v>
-      </c>
-      <c r="S70" t="n">
-        <v>3032.401304347826</v>
-      </c>
-      <c r="T70" t="n">
-        <v>94.29217051775099</v>
-      </c>
-      <c r="U70" t="n">
-        <v>-0.07642670399442597</v>
-      </c>
-      <c r="V70" t="n">
         <v>0.01345981402579843</v>
       </c>
     </row>
@@ -5238,54 +3966,36 @@
         <v>18</v>
       </c>
       <c r="F71" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>18</v>
+        <v>16.26086956521739</v>
       </c>
       <c r="H71" t="n">
-        <v>18</v>
+        <v>0.6887004431501822</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>25.02</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>27.03</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="L71" t="n">
-        <v>18</v>
+        <v>0.01168668720803856</v>
       </c>
       <c r="M71" t="n">
-        <v>16.26086956521739</v>
+        <v>2799.536818181818</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6887004431501822</v>
+        <v>79.03172168345502</v>
       </c>
       <c r="O71" t="n">
-        <v>25.02</v>
+        <v>-0.09720713018063898</v>
       </c>
       <c r="P71" t="n">
-        <v>27.03</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.01168668720803856</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2799.536818181818</v>
-      </c>
-      <c r="T71" t="n">
-        <v>79.03172168345502</v>
-      </c>
-      <c r="U71" t="n">
-        <v>-0.09720713018063898</v>
-      </c>
-      <c r="V71" t="n">
         <v>0.01423401624295071</v>
       </c>
     </row>
@@ -5306,54 +4016,36 @@
         <v>18.52380952380953</v>
       </c>
       <c r="F72" t="n">
-        <v>19</v>
+        <v>0.5117663157191595</v>
       </c>
       <c r="G72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H72" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>30.56</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>8.009999999999998</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5117663157191595</v>
+        <v>5.239999999999998</v>
       </c>
       <c r="L72" t="n">
-        <v>18.52380952380953</v>
+        <v>0.01126595562931354</v>
       </c>
       <c r="M72" t="n">
-        <v>18</v>
+        <v>2720.719047619048</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>105.91677751446</v>
       </c>
       <c r="O72" t="n">
-        <v>30.56</v>
+        <v>0.1227824774957074</v>
       </c>
       <c r="P72" t="n">
-        <v>8.009999999999998</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>5.239999999999998</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0.01126595562931354</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2720.719047619048</v>
-      </c>
-      <c r="T72" t="n">
-        <v>105.91677751446</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0.1227824774957074</v>
-      </c>
-      <c r="V72" t="n">
         <v>0.01756016039991735</v>
       </c>
     </row>
@@ -5374,54 +4066,36 @@
         <v>19.34782608695652</v>
       </c>
       <c r="F73" t="n">
-        <v>19</v>
+        <v>0.7751067757631785</v>
       </c>
       <c r="G73" t="n">
-        <v>21</v>
+        <v>18.52380952380953</v>
       </c>
       <c r="H73" t="n">
-        <v>19</v>
+        <v>0.5117663157191595</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>21.21</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>23.06</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7751067757631785</v>
+        <v>1.620000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>19.34782608695652</v>
+        <v>0.01192325535589123</v>
       </c>
       <c r="M73" t="n">
-        <v>18.52380952380953</v>
+        <v>2733.913913043478</v>
       </c>
       <c r="N73" t="n">
-        <v>0.5117663157191595</v>
+        <v>76.26207139851432</v>
       </c>
       <c r="O73" t="n">
-        <v>21.21</v>
+        <v>-0.09025332333637748</v>
       </c>
       <c r="P73" t="n">
-        <v>23.06</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>1.620000000000001</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.01192325535589123</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2733.913913043478</v>
-      </c>
-      <c r="T73" t="n">
-        <v>76.26207139851432</v>
-      </c>
-      <c r="U73" t="n">
-        <v>-0.09025332333637748</v>
-      </c>
-      <c r="V73" t="n">
         <v>0.01141310886295815</v>
       </c>
     </row>
@@ -5442,54 +4116,36 @@
         <v>21</v>
       </c>
       <c r="F74" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>21</v>
+        <v>19.34782608695652</v>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>0.7751067757631785</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>26.61</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1.469999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>21</v>
+        <v>0.01193152057448166</v>
       </c>
       <c r="M74" t="n">
-        <v>19.34782608695652</v>
+        <v>2634.62</v>
       </c>
       <c r="N74" t="n">
-        <v>0.7751067757631785</v>
+        <v>93.72817009842898</v>
       </c>
       <c r="O74" t="n">
-        <v>26.61</v>
+        <v>0.001277813812041062</v>
       </c>
       <c r="P74" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1.469999999999999</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.01193152057448166</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2634.62</v>
-      </c>
-      <c r="T74" t="n">
-        <v>93.72817009842898</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.001277813812041062</v>
-      </c>
-      <c r="V74" t="n">
         <v>0.0164496972700753</v>
       </c>
     </row>
@@ -5510,54 +4166,36 @@
         <v>21</v>
       </c>
       <c r="F75" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>21</v>
       </c>
       <c r="H75" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>15.76</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>21.47</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1.130000000000003</v>
       </c>
       <c r="L75" t="n">
-        <v>21</v>
+        <v>0.01233830370713318</v>
       </c>
       <c r="M75" t="n">
-        <v>21</v>
+        <v>2583.033636363636</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>141.2575348700941</v>
       </c>
       <c r="O75" t="n">
-        <v>15.76</v>
+        <v>0.1145457216419123</v>
       </c>
       <c r="P75" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.130000000000003</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.01233830370713318</v>
-      </c>
-      <c r="S75" t="n">
-        <v>2583.033636363636</v>
-      </c>
-      <c r="T75" t="n">
-        <v>141.2575348700941</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0.1145457216419123</v>
-      </c>
-      <c r="V75" t="n">
         <v>0.02487247818140731</v>
       </c>
     </row>
@@ -5578,54 +4216,36 @@
         <v>21</v>
       </c>
       <c r="F76" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>21</v>
       </c>
       <c r="H76" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>26.49</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>23.12</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>2.639999999999997</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>0.01276910238125395</v>
       </c>
       <c r="M76" t="n">
-        <v>21</v>
+        <v>2895.459</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>58.98523891172816</v>
       </c>
       <c r="O76" t="n">
-        <v>26.49</v>
+        <v>0.04228389605798122</v>
       </c>
       <c r="P76" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2.639999999999997</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.01276910238125395</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2895.459</v>
-      </c>
-      <c r="T76" t="n">
-        <v>58.98523891172816</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.04228389605798122</v>
-      </c>
-      <c r="V76" t="n">
         <v>0.01354688819517796</v>
       </c>
     </row>
@@ -5646,54 +4266,36 @@
         <v>21</v>
       </c>
       <c r="F77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>21</v>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>27.54</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>11.28</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L77" t="n">
-        <v>21</v>
+        <v>0.01281207157693998</v>
       </c>
       <c r="M77" t="n">
-        <v>21</v>
+        <v>3145.586</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>152.7985287680619</v>
       </c>
       <c r="O77" t="n">
-        <v>27.54</v>
+        <v>0.09374369910155589</v>
       </c>
       <c r="P77" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0.01281207157693998</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3145.586</v>
-      </c>
-      <c r="T77" t="n">
-        <v>152.7985287680619</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0.09374369910155589</v>
-      </c>
-      <c r="V77" t="n">
         <v>0.0180203901375043</v>
       </c>
     </row>
@@ -5714,54 +4316,36 @@
         <v>21</v>
       </c>
       <c r="F78" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>21</v>
       </c>
       <c r="H78" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>29.63</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>24.12</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>2.379999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>21</v>
+        <v>0.01281902591865447</v>
       </c>
       <c r="M78" t="n">
-        <v>21</v>
+        <v>3175.607142857143</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>68.53531521360746</v>
       </c>
       <c r="O78" t="n">
-        <v>29.63</v>
+        <v>-0.04207926300095677</v>
       </c>
       <c r="P78" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>2.379999999999999</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.01281902591865447</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3175.607142857143</v>
-      </c>
-      <c r="T78" t="n">
-        <v>68.53531521360746</v>
-      </c>
-      <c r="U78" t="n">
-        <v>-0.04207926300095677</v>
-      </c>
-      <c r="V78" t="n">
         <v>0.01398660657956558</v>
       </c>
     </row>
@@ -5782,54 +4366,36 @@
         <v>21</v>
       </c>
       <c r="F79" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>21</v>
       </c>
       <c r="H79" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>30.16</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>2.949999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>0.01234012412924823</v>
       </c>
       <c r="M79" t="n">
-        <v>21</v>
+        <v>2870.904545454545</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>97.31111455764041</v>
       </c>
       <c r="O79" t="n">
-        <v>30.16</v>
+        <v>-0.01550382366930569</v>
       </c>
       <c r="P79" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>2.949999999999999</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.01234012412924823</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2870.904545454545</v>
-      </c>
-      <c r="T79" t="n">
-        <v>97.31111455764041</v>
-      </c>
-      <c r="U79" t="n">
-        <v>-0.01550382366930569</v>
-      </c>
-      <c r="V79" t="n">
         <v>0.01936594170509362</v>
       </c>
     </row>
@@ -5850,54 +4416,36 @@
         <v>21</v>
       </c>
       <c r="F80" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>21</v>
       </c>
       <c r="H80" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>27.98999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>24.49</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4.240000000000002</v>
       </c>
       <c r="L80" t="n">
-        <v>21</v>
+        <v>0.01210951789996662</v>
       </c>
       <c r="M80" t="n">
-        <v>21</v>
+        <v>2824.417</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>62.7598883045533</v>
       </c>
       <c r="O80" t="n">
-        <v>27.98999999999999</v>
+        <v>-0.00277435047766772</v>
       </c>
       <c r="P80" t="n">
-        <v>24.49</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>4.240000000000002</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.01210951789996662</v>
-      </c>
-      <c r="S80" t="n">
-        <v>2824.417</v>
-      </c>
-      <c r="T80" t="n">
-        <v>62.7598883045533</v>
-      </c>
-      <c r="U80" t="n">
-        <v>-0.00277435047766772</v>
-      </c>
-      <c r="V80" t="n">
         <v>0.01854433821511479</v>
       </c>
     </row>
@@ -5918,54 +4466,36 @@
         <v>20.25</v>
       </c>
       <c r="F81" t="n">
-        <v>20</v>
+        <v>0.4442616583193181</v>
       </c>
       <c r="G81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>22.21</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>8.909999999999997</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4442616583193181</v>
+        <v>5.25</v>
       </c>
       <c r="L81" t="n">
-        <v>20.25</v>
+        <v>0.01219430351518236</v>
       </c>
       <c r="M81" t="n">
-        <v>21</v>
+        <v>2784.32</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>41.31872074750776</v>
       </c>
       <c r="O81" t="n">
-        <v>22.21</v>
+        <v>0.006258680340817113</v>
       </c>
       <c r="P81" t="n">
-        <v>8.909999999999997</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.01219430351518236</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2784.32</v>
-      </c>
-      <c r="T81" t="n">
-        <v>41.31872074750776</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0.006258680340817113</v>
-      </c>
-      <c r="V81" t="n">
         <v>0.01054418667519808</v>
       </c>
     </row>
@@ -5986,54 +4516,36 @@
         <v>19.65217391304348</v>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>0.7751067757631785</v>
       </c>
       <c r="G82" t="n">
-        <v>18</v>
+        <v>20.25</v>
       </c>
       <c r="H82" t="n">
-        <v>18</v>
+        <v>0.4442616583193181</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>17.78</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>25.75</v>
       </c>
       <c r="K82" t="n">
-        <v>0.7751067757631785</v>
+        <v>7.329999999999998</v>
       </c>
       <c r="L82" t="n">
-        <v>19.65217391304348</v>
+        <v>0.01171880240956247</v>
       </c>
       <c r="M82" t="n">
-        <v>20.25</v>
+        <v>2768.78</v>
       </c>
       <c r="N82" t="n">
-        <v>0.4442616583193181</v>
+        <v>50.68368376509365</v>
       </c>
       <c r="O82" t="n">
-        <v>17.78</v>
+        <v>-0.04083638763674158</v>
       </c>
       <c r="P82" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>7.329999999999998</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.01171880240956247</v>
-      </c>
-      <c r="S82" t="n">
-        <v>2768.78</v>
-      </c>
-      <c r="T82" t="n">
-        <v>50.68368376509365</v>
-      </c>
-      <c r="U82" t="n">
-        <v>-0.04083638763674158</v>
-      </c>
-      <c r="V82" t="n">
         <v>0.01390505859545336</v>
       </c>
     </row>
@@ -6054,54 +4566,36 @@
         <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>18</v>
+        <v>19.65217391304348</v>
       </c>
       <c r="H83" t="n">
-        <v>18</v>
+        <v>0.7751067757631785</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>31.04</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>27.61</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>8.099999999999998</v>
       </c>
       <c r="L83" t="n">
-        <v>18</v>
+        <v>0.0125065769025734</v>
       </c>
       <c r="M83" t="n">
-        <v>19.65217391304348</v>
+        <v>2899.633809523809</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7751067757631785</v>
+        <v>77.90832943120967</v>
       </c>
       <c r="O83" t="n">
-        <v>31.04</v>
+        <v>0.062830372656691</v>
       </c>
       <c r="P83" t="n">
-        <v>27.61</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>8.099999999999998</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.0125065769025734</v>
-      </c>
-      <c r="S83" t="n">
-        <v>2899.633809523809</v>
-      </c>
-      <c r="T83" t="n">
-        <v>77.90832943120967</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0.062830372656691</v>
-      </c>
-      <c r="V83" t="n">
         <v>0.01315300536851439</v>
       </c>
     </row>
@@ -6122,54 +4616,36 @@
         <v>17.45454545454545</v>
       </c>
       <c r="F84" t="n">
-        <v>17</v>
+        <v>0.509647191437626</v>
       </c>
       <c r="G84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>28.53</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>14.12</v>
       </c>
       <c r="K84" t="n">
-        <v>0.509647191437626</v>
+        <v>8.09</v>
       </c>
       <c r="L84" t="n">
-        <v>17.45454545454545</v>
+        <v>0.01149633221713131</v>
       </c>
       <c r="M84" t="n">
-        <v>18</v>
+        <v>2813.168181818182</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>81.74794674202427</v>
       </c>
       <c r="O84" t="n">
-        <v>28.53</v>
+        <v>-0.07009771490524663</v>
       </c>
       <c r="P84" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0.01149633221713131</v>
-      </c>
-      <c r="S84" t="n">
-        <v>2813.168181818182</v>
-      </c>
-      <c r="T84" t="n">
-        <v>81.74794674202427</v>
-      </c>
-      <c r="U84" t="n">
-        <v>-0.07009771490524663</v>
-      </c>
-      <c r="V84" t="n">
         <v>0.009192618189897639</v>
       </c>
     </row>
@@ -6190,54 +4666,36 @@
         <v>16.89130434782609</v>
       </c>
       <c r="F85" t="n">
-        <v>17</v>
+        <v>0.2108705839183244</v>
       </c>
       <c r="G85" t="n">
-        <v>16.5</v>
+        <v>17.45454545454545</v>
       </c>
       <c r="H85" t="n">
-        <v>16.5</v>
+        <v>0.509647191437626</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>35.66</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5</v>
+        <v>25.02</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2108705839183244</v>
+        <v>7.81</v>
       </c>
       <c r="L85" t="n">
-        <v>16.89130434782609</v>
+        <v>0.01104341958050647</v>
       </c>
       <c r="M85" t="n">
-        <v>17.45454545454545</v>
+        <v>2595.877391304348</v>
       </c>
       <c r="N85" t="n">
-        <v>0.509647191437626</v>
+        <v>68.41723262569229</v>
       </c>
       <c r="O85" t="n">
-        <v>35.66</v>
+        <v>-0.04610444801208813</v>
       </c>
       <c r="P85" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.01104341958050647</v>
-      </c>
-      <c r="S85" t="n">
-        <v>2595.877391304348</v>
-      </c>
-      <c r="T85" t="n">
-        <v>68.41723262569229</v>
-      </c>
-      <c r="U85" t="n">
-        <v>-0.04610444801208813</v>
-      </c>
-      <c r="V85" t="n">
         <v>0.02149344746084847</v>
       </c>
     </row>
@@ -6258,54 +4716,36 @@
         <v>16.5</v>
       </c>
       <c r="F86" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5</v>
+        <v>16.89130434782609</v>
       </c>
       <c r="H86" t="n">
-        <v>16.5</v>
+        <v>0.2108705839183244</v>
       </c>
       <c r="I86" t="n">
-        <v>16.5</v>
+        <v>31.1</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>9.779999999999998</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>7.199999999999998</v>
       </c>
       <c r="L86" t="n">
-        <v>16.5</v>
+        <v>0.01134099625171792</v>
       </c>
       <c r="M86" t="n">
-        <v>16.89130434782609</v>
+        <v>2591.471</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2108705839183244</v>
+        <v>59.69532212123426</v>
       </c>
       <c r="O86" t="n">
-        <v>31.1</v>
+        <v>0.05676245528416768</v>
       </c>
       <c r="P86" t="n">
-        <v>9.779999999999998</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>7.199999999999998</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0.01134099625171792</v>
-      </c>
-      <c r="S86" t="n">
-        <v>2591.471</v>
-      </c>
-      <c r="T86" t="n">
-        <v>59.69532212123426</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0.05676245528416768</v>
-      </c>
-      <c r="V86" t="n">
         <v>0.0136388534842457</v>
       </c>
     </row>
@@ -6326,54 +4766,36 @@
         <v>16.34090909090909</v>
       </c>
       <c r="F87" t="n">
+        <v>0.2383656473113982</v>
+      </c>
+      <c r="G87" t="n">
         <v>16.5</v>
       </c>
-      <c r="G87" t="n">
-        <v>16</v>
-      </c>
       <c r="H87" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>16.5</v>
+        <v>19.08</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5</v>
+        <v>27.29</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2383656473113982</v>
+        <v>7.459999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>16.34090909090909</v>
+        <v>0.01137529276183336</v>
       </c>
       <c r="M87" t="n">
-        <v>16.5</v>
+        <v>2723.151363636364</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>34.52357404323348</v>
       </c>
       <c r="O87" t="n">
-        <v>19.08</v>
+        <v>0.02965838335944748</v>
       </c>
       <c r="P87" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>7.459999999999999</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.01137529276183336</v>
-      </c>
-      <c r="S87" t="n">
-        <v>2723.151363636364</v>
-      </c>
-      <c r="T87" t="n">
-        <v>34.52357404323348</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0.02965838335944748</v>
-      </c>
-      <c r="V87" t="n">
         <v>0.007652214389754769</v>
       </c>
     </row>
@@ -6394,48 +4816,30 @@
         <v>16</v>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>16</v>
+        <v>16.34090909090909</v>
       </c>
       <c r="H88" t="n">
-        <v>16</v>
-      </c>
-      <c r="I88" t="n">
-        <v>16</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2383656473113982</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
-        <v>16</v>
+        <v>0.01134762103812315</v>
       </c>
       <c r="M88" t="n">
-        <v>16.34090909090909</v>
+        <v>2747.612631578947</v>
       </c>
       <c r="N88" t="n">
-        <v>0.2383656473113982</v>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="n">
-        <v>0.01134762103812315</v>
-      </c>
-      <c r="S88" t="n">
-        <v>2747.612631578947</v>
-      </c>
-      <c r="T88" t="n">
         <v>32.76829138767884</v>
       </c>
-      <c r="U88" t="n">
+      <c r="O88" t="n">
         <v>0.009303287161463558</v>
       </c>
-      <c r="V88" t="n">
+      <c r="P88" t="n">
         <v>0.005962446576861836</v>
       </c>
     </row>
@@ -6454,46 +4858,28 @@
         <v>15.83333333333333</v>
       </c>
       <c r="F89" t="n">
+        <v>0.2439750182371336</v>
+      </c>
+      <c r="G89" t="n">
         <v>16</v>
       </c>
-      <c r="G89" t="n">
-        <v>15.5</v>
-      </c>
       <c r="H89" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I89" t="n">
-        <v>16</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.2439750182371336</v>
-      </c>
-      <c r="L89" t="n">
-        <v>15.83333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>16</v>
+        <v>2761.764</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>2761.764</v>
-      </c>
-      <c r="T89" t="n">
         <v>22.24195578502171</v>
       </c>
-      <c r="U89" t="n">
+      <c r="O89" t="n">
         <v>0.004348831161325784</v>
       </c>
-      <c r="V89" t="n">
+      <c r="P89" t="n">
         <v>0.006707859815548966</v>
       </c>
     </row>
